--- a/references/clearance/COA-public.xlsx
+++ b/references/clearance/COA-public.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,40 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +66,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,190 +469,244 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>{{COMPANY_NAME_EN}}</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>{{COMPANY_ADDR_EN}}</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>{{COMPANY_TEL_EN}}</t>
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>CERTIFICATE OF ANALYSIS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>PRODUCT NAME: {{PRODUCT_NAME}}</t>
         </is>
       </c>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>QUANTITY: {{SHIPPED_QTY}}</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BATCH NO.: {{BATCH_NO}}</t>
         </is>
       </c>
+      <c r="D8" s="2" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>PRODUCTION DATE: {{PROD_DATE}}</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>EXPIRATION DATE: {{EXP_DATE}}</t>
         </is>
       </c>
+      <c r="D9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>PI No.: {{COA_PI_NO}}</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>TESTS</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>ITEM</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>SPECIFICATIONS</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>RESULTS</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>SENSORY REQUIREMENTS</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>APPEARANCE</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>{{APPEARANCE_SPEC}}</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>{{APPEARANCE_RESULT}}</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>PHYSICOCHEMICAL REQUIREMENT</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>{{SOLID_LABEL}}</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>{{SOLID_SPEC}}</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>{{SOLID_RESULT}}</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr">
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>{{PH_LABEL}}</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>{{PH_SPEC}}</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>{{PH_RESULT}}</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr"/>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>CONSEQUENCE</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>THE PRODUCT IS CONFORMED TO THESE STANDARD OF GB/T19001-2008 AND GB/T24001-2004.</t>
         </is>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>MAKER: {{COMPANY_NAME_EN}}</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>THE CENTER OF QUALITY INSPECTION</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>{{COMPANY_NAME_EN}}</t>
         </is>
       </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A12"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="C8:D8"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>